--- a/doc/4-0AEO认证的评分规则20200708--通用 高级认证以及一般认证.xlsx
+++ b/doc/4-0AEO认证的评分规则20200708--通用 高级认证以及一般认证.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Air\Desktop\Winlison\19-关务管理系统2018\201904 holly业务需求整理\2-进销存以及AEO管理平台\1-AEO平台以及内部进销存管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\aeo_cms\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22088696-0F5A-40FC-B779-A625DB4684E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F202381-8BFB-4658-B5AD-29AE5DDFDBA2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{511F7259-C8DE-46D1-8621-C33646C8FDBB}"/>
+    <workbookView xWindow="255" yWindow="375" windowWidth="25740" windowHeight="11385" tabRatio="707" activeTab="1" xr2:uid="{511F7259-C8DE-46D1-8621-C33646C8FDBB}"/>
   </bookViews>
   <sheets>
     <sheet name="功能清单" sheetId="1" r:id="rId1"/>
@@ -22,23 +22,17 @@
     <sheet name="表体5-贸易安全标准1" sheetId="5" r:id="rId7"/>
     <sheet name="表体6-贸易安全标准2" sheetId="14" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="409">
   <si>
     <t>AEO高认自评</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -521,14 +515,6 @@
   </si>
   <si>
     <t>满足/不满足</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YES，有变化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1133,18 +1119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>进出口业务规范</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16-注册信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18-申报规范</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>海关管理要求</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1579,33 +1553,6 @@
   <si>
     <t>E292</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>法定代表人（负责人）、负责关务的高级管理人员、关务负责人、负责贸易安全的高级管理人员应当每年参加2次以上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【高认2次以上，一般认证1次以上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>】海关法律法规等相关规定的内部培训，及时了解、掌握相关管理规定。</t>
-    </r>
   </si>
   <si>
     <t>高认：已成为高级认证企业的，应当每年对持续符合海关高级认证企业标准实施内部审计。
@@ -1799,12 +1746,40 @@
     <t>30-危机管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>法定代表人（负责人）、负责关务的高级管理人员、关务负责人、负责贸易安全的高级管理人员应当每年参加2次以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【高认2次以上，一般认证1次以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>】海关法律法规等相关规定的内部培训，及时了解、掌握相关管理规定。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2317,6 +2292,108 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2325,108 +2402,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2742,8 +2717,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4EDAE0-CA3F-4454-A2F1-02009836762E}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.375" style="1" customWidth="1"/>
@@ -2751,7 +2727,7 @@
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">
         <v>111</v>
       </c>
@@ -2759,7 +2735,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2767,7 +2743,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="B3" s="40" t="s">
         <v>1</v>
       </c>
@@ -2775,17 +2751,17 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="B4" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="B5" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>110</v>
       </c>
@@ -2793,7 +2769,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="B7" s="40" t="s">
         <v>1</v>
       </c>
@@ -2801,12 +2777,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="B8" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="B9" s="1" t="s">
         <v>108</v>
       </c>
@@ -2819,11 +2795,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{536C297E-90D5-4B5E-AAAC-4025A07ABA8F}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:H43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
@@ -2835,7 +2811,7 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="5" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -2849,13 +2825,13 @@
       <c r="G1" s="2"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="B2" s="7"/>
       <c r="D2" s="7"/>
       <c r="F2" s="8"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -2881,7 +2857,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>11</v>
       </c>
@@ -2893,7 +2869,7 @@
       <c r="G4" s="10"/>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="38.25">
       <c r="A5" s="9" t="s">
         <v>12</v>
       </c>
@@ -2919,7 +2895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="38.25">
       <c r="A6" s="9" t="s">
         <v>78</v>
       </c>
@@ -2945,7 +2921,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="25.5">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
@@ -2971,7 +2947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="30" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>21</v>
       </c>
@@ -2979,7 +2955,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
@@ -2991,7 +2967,7 @@
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
     </row>
-    <row r="10" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="21" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>114</v>
       </c>
@@ -3009,18 +2985,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="9.75" customHeight="1">
       <c r="A11" s="2"/>
       <c r="C11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="18" customHeight="1">
       <c r="A12" s="23" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="36"/>
       <c r="C12" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="26"/>
@@ -3028,11 +3004,11 @@
       <c r="G12" s="26"/>
       <c r="H12" s="27"/>
     </row>
-    <row r="13" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="69"/>
+    <row r="13" spans="1:8" ht="20.25" customHeight="1">
+      <c r="A13" s="54"/>
       <c r="B13" s="32"/>
       <c r="C13" s="28" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D13" s="29"/>
       <c r="E13" s="28"/>
@@ -3040,11 +3016,11 @@
       <c r="G13" s="28"/>
       <c r="H13" s="29"/>
     </row>
-    <row r="14" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="69"/>
+    <row r="14" spans="1:8" ht="20.25" customHeight="1">
+      <c r="A14" s="54"/>
       <c r="B14" s="32"/>
       <c r="C14" s="28" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D14" s="29"/>
       <c r="E14" s="28"/>
@@ -3052,8 +3028,8 @@
       <c r="G14" s="28"/>
       <c r="H14" s="29"/>
     </row>
-    <row r="15" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="69"/>
+    <row r="15" spans="1:8" ht="11.25" customHeight="1">
+      <c r="A15" s="54"/>
       <c r="B15" s="32"/>
       <c r="C15" s="28"/>
       <c r="D15" s="29"/>
@@ -3062,8 +3038,8 @@
       <c r="G15" s="28"/>
       <c r="H15" s="29"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="69"/>
+    <row r="16" spans="1:8">
+      <c r="A16" s="54"/>
       <c r="B16" s="32"/>
       <c r="C16" s="35" t="s">
         <v>25</v>
@@ -3078,61 +3054,61 @@
       </c>
       <c r="H16" s="29"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8">
       <c r="A17" s="24"/>
       <c r="B17" s="32"/>
       <c r="C17" s="28" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D17" s="29"/>
       <c r="E17" s="28" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F17" s="29"/>
       <c r="G17" s="28" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H17" s="29"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8">
       <c r="A18" s="24"/>
       <c r="B18" s="32"/>
       <c r="C18" s="28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D18" s="29"/>
       <c r="E18" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F18" s="29"/>
       <c r="G18" s="28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H18" s="29"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8">
       <c r="A19" s="25"/>
       <c r="B19" s="33"/>
       <c r="C19" s="30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D19" s="31"/>
       <c r="E19" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H19" s="31"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8">
       <c r="A21" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B21" s="34"/>
       <c r="C21" s="26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="36"/>
@@ -3140,11 +3116,11 @@
       <c r="G21" s="36"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="69"/>
+    <row r="22" spans="1:8">
+      <c r="A22" s="54"/>
       <c r="B22" s="24"/>
       <c r="C22" s="28" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D22" s="29"/>
       <c r="E22" s="32"/>
@@ -3152,11 +3128,11 @@
       <c r="G22" s="32"/>
       <c r="H22" s="29"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8">
       <c r="A23" s="25"/>
       <c r="B23" s="25"/>
       <c r="C23" s="30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33"/>
@@ -3164,17 +3140,17 @@
       <c r="G23" s="33"/>
       <c r="H23" s="31"/>
     </row>
-    <row r="24" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="9.75" customHeight="1">
       <c r="A24" s="2"/>
       <c r="C24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="67" t="s">
+    <row r="25" spans="1:8">
+      <c r="A25" s="52" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="34"/>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="57" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="27"/>
@@ -3187,129 +3163,129 @@
       </c>
       <c r="H25" s="27"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8">
       <c r="A26" s="32"/>
       <c r="B26" s="24"/>
-      <c r="C26" s="73" t="s">
-        <v>151</v>
+      <c r="C26" s="58" t="s">
+        <v>149</v>
       </c>
       <c r="D26" s="29"/>
       <c r="E26" s="28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F26" s="29"/>
       <c r="G26" s="28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H26" s="29"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8">
       <c r="A27" s="32"/>
       <c r="B27" s="24"/>
-      <c r="C27" s="73" t="s">
-        <v>150</v>
+      <c r="C27" s="58" t="s">
+        <v>148</v>
       </c>
       <c r="D27" s="29"/>
       <c r="E27" s="28" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F27" s="29"/>
       <c r="G27" s="28" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H27" s="29"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8">
       <c r="A28" s="32"/>
       <c r="B28" s="24"/>
-      <c r="C28" s="74"/>
+      <c r="C28" s="59"/>
       <c r="D28" s="31"/>
       <c r="E28" s="30" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F28" s="31"/>
       <c r="G28" s="33"/>
       <c r="H28" s="31"/>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="71"/>
+    <row r="29" spans="1:8" ht="18" customHeight="1">
+      <c r="A29" s="56"/>
       <c r="B29" s="24"/>
-      <c r="C29" s="72" t="s">
-        <v>157</v>
+      <c r="C29" s="57" t="s">
+        <v>155</v>
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F29" s="27"/>
       <c r="G29" s="36"/>
       <c r="H29" s="27"/>
     </row>
-    <row r="30" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="68"/>
+    <row r="30" spans="1:8" ht="20.25" customHeight="1">
+      <c r="A30" s="53"/>
       <c r="B30" s="25"/>
-      <c r="C30" s="74" t="s">
-        <v>159</v>
+      <c r="C30" s="59" t="s">
+        <v>157</v>
       </c>
       <c r="D30" s="31"/>
       <c r="E30" s="30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="33"/>
       <c r="H30" s="31"/>
     </row>
-    <row r="31" spans="1:8" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="9.75" customHeight="1">
       <c r="A31" s="2"/>
       <c r="C31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="67" t="s">
+    <row r="32" spans="1:8">
+      <c r="A32" s="52" t="s">
         <v>67</v>
       </c>
       <c r="B32" s="34"/>
-      <c r="C32" s="72" t="s">
+      <c r="C32" s="57" t="s">
         <v>69</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F32" s="27"/>
       <c r="G32" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H32" s="27"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8">
       <c r="A33" s="32"/>
       <c r="B33" s="24"/>
-      <c r="C33" s="73" t="s">
-        <v>163</v>
+      <c r="C33" s="58" t="s">
+        <v>161</v>
       </c>
       <c r="D33" s="29"/>
       <c r="E33" s="28" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F33" s="29"/>
       <c r="G33" s="28" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H33" s="29"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8">
       <c r="A34" s="32"/>
       <c r="B34" s="24"/>
-      <c r="C34" s="73"/>
+      <c r="C34" s="58"/>
       <c r="D34" s="29"/>
       <c r="E34" s="28"/>
       <c r="F34" s="29"/>
       <c r="G34" s="28"/>
       <c r="H34" s="29"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="71"/>
+    <row r="35" spans="1:8">
+      <c r="A35" s="56"/>
       <c r="B35" s="24"/>
       <c r="C35" s="26" t="s">
         <v>68</v>
@@ -3319,38 +3295,38 @@
         <v>71</v>
       </c>
       <c r="F35" s="27"/>
-      <c r="G35" s="75" t="s">
+      <c r="G35" s="60" t="s">
         <v>72</v>
       </c>
       <c r="H35" s="27"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8">
       <c r="A36" s="32"/>
       <c r="B36" s="24"/>
       <c r="C36" s="28" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D36" s="29"/>
       <c r="E36" s="28" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F36" s="29"/>
-      <c r="G36" s="74" t="s">
-        <v>171</v>
+      <c r="G36" s="59" t="s">
+        <v>169</v>
       </c>
       <c r="H36" s="29"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8">
       <c r="A37" s="32"/>
       <c r="B37" s="24"/>
-      <c r="C37" s="70"/>
+      <c r="C37" s="55"/>
       <c r="D37" s="29"/>
       <c r="E37" s="32"/>
       <c r="F37" s="29"/>
       <c r="G37" s="32"/>
       <c r="H37" s="29"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8">
       <c r="A38" s="32"/>
       <c r="B38" s="24"/>
       <c r="C38" s="35" t="s">
@@ -3358,27 +3334,27 @@
       </c>
       <c r="D38" s="29"/>
       <c r="E38" s="35" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="F38" s="29"/>
       <c r="G38" s="32"/>
       <c r="H38" s="29"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8">
       <c r="A39" s="33"/>
       <c r="B39" s="25"/>
       <c r="C39" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D39" s="31"/>
       <c r="E39" s="33" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="F39" s="31"/>
       <c r="G39" s="33"/>
       <c r="H39" s="31"/>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1">
       <c r="A41" s="10" t="s">
         <v>31</v>
       </c>
@@ -3390,7 +3366,7 @@
       <c r="G41" s="10"/>
       <c r="H41" s="11"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8">
       <c r="A42" s="6" t="s">
         <v>32</v>
       </c>
@@ -3404,7 +3380,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8">
       <c r="A43" s="6" t="s">
         <v>35</v>
       </c>
@@ -3427,8 +3403,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD31C8F-5C61-4CDD-88AF-89C3EC68C004}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
@@ -3439,7 +3416,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="5" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -3454,7 +3431,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="6"/>
@@ -3465,7 +3442,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
@@ -3478,47 +3455,47 @@
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="6"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="E6" s="6"/>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="6"/>
       <c r="C8" s="6"/>
       <c r="E8" s="6"/>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="14" t="s">
         <v>41</v>
       </c>
@@ -3528,13 +3505,13 @@
       <c r="C9" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="58" t="s">
+      <c r="D9" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="60"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="71"/>
       <c r="G9" s="45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>18</v>
@@ -3543,9 +3520,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="10"/>
@@ -3556,145 +3533,179 @@
       <c r="H10" s="10"/>
       <c r="I10" s="11"/>
     </row>
-    <row r="11" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="36">
       <c r="A11" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="57"/>
+      <c r="D11" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="73"/>
+      <c r="F11" s="74"/>
       <c r="G11" s="42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I11" s="19"/>
-    </row>
-    <row r="12" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J11" s="1" t="str">
+        <f>_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A11,"&lt;/td&gt;&lt;td&gt;",B11,"&lt;/td&gt;&lt;td&gt;",C11,"&lt;/td&gt;&lt;td&gt;",D11,"&lt;/td&gt;&lt;td&gt;",G11,"&lt;/td&gt;&lt;td&gt;",H11,"&lt;/td&gt;&lt;td&gt;",I11,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;组织机构控制&lt;/td&gt;&lt;td&gt;E010&lt;/td&gt;&lt;td&gt;1-海关业务培训&lt;/td&gt;&lt;td&gt;海关业务培训&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="48">
       <c r="A12" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="E12" s="62"/>
-      <c r="F12" s="63"/>
+        <v>173</v>
+      </c>
+      <c r="D12" s="66" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="67"/>
+      <c r="F12" s="68"/>
       <c r="G12" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I12" s="17"/>
-    </row>
-    <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J12" s="1" t="str">
+        <f t="shared" ref="J12:J27" si="0">_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A12,"&lt;/td&gt;&lt;td&gt;",B12,"&lt;/td&gt;&lt;td&gt;",C12,"&lt;/td&gt;&lt;td&gt;",D12,"&lt;/td&gt;&lt;td&gt;",G12,"&lt;/td&gt;&lt;td&gt;",H12,"&lt;/td&gt;&lt;td&gt;",I12,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;1-海关业务培训&lt;/td&gt;&lt;td&gt;E011&lt;/td&gt;&lt;td&gt;关务管理制度&lt;/td&gt;&lt;td&gt;建立海关法律法规等相关规定的内部培训制度并有效落实。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="48">
       <c r="A13" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D13" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="E13" s="62"/>
-      <c r="F13" s="63"/>
+        <v>129</v>
+      </c>
+      <c r="D13" s="66" t="s">
+        <v>408</v>
+      </c>
+      <c r="E13" s="67"/>
+      <c r="F13" s="68"/>
       <c r="G13" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;1-海关业务培训&lt;/td&gt;&lt;td&gt;E012&lt;/td&gt;&lt;td&gt;海关业务培训&lt;/td&gt;&lt;td&gt;法定代表人（负责人）、负责关务的高级管理人员、关务负责人、负责贸易安全的高级管理人员应当每年参加2次以上【高认2次以上，一般认证1次以上】海关法律法规等相关规定的内部培训，及时了解、掌握相关管理规定。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="36">
       <c r="A14" s="20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C14" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="57"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
       <c r="G14" s="42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A15" s="81" t="s">
-        <v>180</v>
-      </c>
-      <c r="B15" s="82" t="s">
+      <c r="J14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;组织机构控制&lt;/td&gt;&lt;td&gt;E020&lt;/td&gt;&lt;td&gt;2-内部组织架构&lt;/td&gt;&lt;td&gt;组织机构&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="48">
+      <c r="A15" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="B15" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" s="61" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="81" t="s">
-        <v>186</v>
-      </c>
-      <c r="D15" s="83" t="s">
+      <c r="D15" s="75" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" s="76"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="65"/>
+      <c r="J15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;2-内部组织架构&lt;/td&gt;&lt;td&gt;E021&lt;/td&gt;&lt;td&gt;岗位职责&lt;/td&gt;&lt;td&gt;进出口业务、财务、贸易安全、内部审计等部门（岗位）职责分工明确并有效落实。&lt;/td&gt;&lt;td&gt;一般认证无&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="48">
+      <c r="A16" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="E15" s="84"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="86" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15" s="87" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="88"/>
-    </row>
-    <row r="16" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="D16" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="68"/>
       <c r="G16" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I16" s="17"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;2-内部组织架构&lt;/td&gt;&lt;td&gt;E022&lt;/td&gt;&lt;td&gt;高级管理人员&lt;/td&gt;&lt;td&gt;指定高级管理人员负责关务。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="10" t="s">
         <v>61</v>
       </c>
@@ -3706,236 +3717,297 @@
       <c r="G17" s="11"/>
       <c r="H17" s="10"/>
       <c r="I17" s="11"/>
-    </row>
-    <row r="18" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;内部控制标准-达标-0/基本达标-1/不达标-2/不适用-&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="36">
       <c r="A18" s="20" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="56"/>
-      <c r="F18" s="57"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="74"/>
       <c r="G18" s="42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H18" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务控制&lt;/td&gt;&lt;td&gt;E030&lt;/td&gt;&lt;td&gt;3-单证控制&lt;/td&gt;&lt;td&gt;单证控制&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="48">
       <c r="A19" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="D19" s="61" t="s">
-        <v>190</v>
-      </c>
-      <c r="E19" s="62"/>
-      <c r="F19" s="63"/>
+        <v>206</v>
+      </c>
+      <c r="D19" s="66" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="67"/>
+      <c r="F19" s="68"/>
       <c r="G19" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H19" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I19" s="17"/>
-    </row>
-    <row r="20" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;3-单证控制&lt;/td&gt;&lt;td&gt;E031&lt;/td&gt;&lt;td&gt;单证复核纠错&lt;/td&gt;&lt;td&gt;建立进出口单证复核或者纠错制度并有效落实。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="36">
       <c r="A20" s="20" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="D20" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="56"/>
-      <c r="F20" s="57"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
       <c r="G20" s="42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H20" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I20" s="19"/>
-    </row>
-    <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务控制&lt;/td&gt;&lt;td&gt;E040&lt;/td&gt;&lt;td&gt;4-单证保管&lt;/td&gt;&lt;td&gt;单证保管&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="48">
       <c r="A21" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="E21" s="62"/>
-      <c r="F21" s="63"/>
+        <v>207</v>
+      </c>
+      <c r="D21" s="66" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" s="67"/>
+      <c r="F21" s="68"/>
       <c r="G21" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;4-单证保管&lt;/td&gt;&lt;td&gt;E041&lt;/td&gt;&lt;td&gt;报关单证&lt;/td&gt;&lt;td&gt;建立符合海关要求的进出口单证管理制度，确保归档信息的及时性、完整性、准确性与安全性。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="48">
       <c r="A22" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="D22" s="61" t="s">
-        <v>195</v>
-      </c>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
+        <v>208</v>
+      </c>
+      <c r="D22" s="66" t="s">
+        <v>193</v>
+      </c>
+      <c r="E22" s="67"/>
+      <c r="F22" s="68"/>
       <c r="G22" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;4-单证保管&lt;/td&gt;&lt;td&gt;E042&lt;/td&gt;&lt;td&gt;特殊物品单证&lt;/td&gt;&lt;td&gt;建立符合海关要求的特殊物品安全管理制度并按照规定留存特殊物品生产、使用、销售记录。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="48">
       <c r="A23" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="D23" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="63"/>
+        <v>209</v>
+      </c>
+      <c r="D23" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" s="67"/>
+      <c r="F23" s="68"/>
       <c r="G23" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H23" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I23" s="17"/>
-    </row>
-    <row r="24" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;4-单证保管&lt;/td&gt;&lt;td&gt;E043&lt;/td&gt;&lt;td&gt;单证保管制度&lt;/td&gt;&lt;td&gt;建立符合海关要求的货物技术标准规范保管制度。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="48">
       <c r="A24" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="D24" s="61" t="s">
-        <v>194</v>
-      </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="63"/>
+        <v>210</v>
+      </c>
+      <c r="D24" s="66" t="s">
+        <v>192</v>
+      </c>
+      <c r="E24" s="67"/>
+      <c r="F24" s="68"/>
       <c r="G24" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H24" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I24" s="17"/>
-    </row>
-    <row r="25" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;4-单证保管&lt;/td&gt;&lt;td&gt;E044&lt;/td&gt;&lt;td&gt;印章证书管理&lt;/td&gt;&lt;td&gt;妥善管理报关专用印章、海关核发的证书、法律文书等单证。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="48">
       <c r="A25" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="D25" s="61" t="s">
-        <v>196</v>
-      </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63"/>
+        <v>211</v>
+      </c>
+      <c r="D25" s="66" t="s">
+        <v>194</v>
+      </c>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68"/>
       <c r="G25" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H25" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I25" s="17"/>
-    </row>
-    <row r="26" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;4-单证保管&lt;/td&gt;&lt;td&gt;E045&lt;/td&gt;&lt;td&gt;纸面电子档案&lt;/td&gt;&lt;td&gt;建立企业认证的书面或者电子资料的专门档案。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="36">
       <c r="A26" s="20" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74"/>
       <c r="G26" s="44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H26" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I26" s="19"/>
-    </row>
-    <row r="27" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A27" s="81" t="s">
-        <v>207</v>
-      </c>
-      <c r="B27" s="82" t="s">
+      <c r="J26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务控制&lt;/td&gt;&lt;td&gt;E050&lt;/td&gt;&lt;td&gt;5-进出口活动&lt;/td&gt;&lt;td&gt;进出口活动&lt;/td&gt;&lt;td&gt;一般认证无&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="48">
+      <c r="A27" s="61" t="s">
         <v>205</v>
       </c>
-      <c r="C27" s="81" t="s">
-        <v>214</v>
-      </c>
-      <c r="D27" s="83" t="s">
-        <v>197</v>
-      </c>
-      <c r="E27" s="84"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="86" t="s">
-        <v>123</v>
-      </c>
-      <c r="H27" s="87" t="s">
+      <c r="B27" s="62" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="D27" s="75" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" s="76"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="H27" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="88"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;5-进出口活动&lt;/td&gt;&lt;td&gt;E051&lt;/td&gt;&lt;td&gt;进出口流程&lt;/td&gt;&lt;td&gt;建立进出口活动的流程管理制度&lt;/td&gt;&lt;td&gt;一般认证无&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -3959,16 +4031,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD9B19D-42BC-4FAE-897C-66F94BCCCFE8}">
-  <sheetPr>
+  <sheetPr codeName="Sheet4">
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
@@ -3982,7 +4055,7 @@
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="5" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -3997,14 +4070,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="B2" s="7"/>
       <c r="D2" s="7"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
@@ -4017,46 +4090,46 @@
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="C5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="14" t="s">
         <v>41</v>
       </c>
@@ -4066,13 +4139,13 @@
       <c r="C9" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="58" t="s">
+      <c r="D9" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="60"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="71"/>
       <c r="G9" s="38" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>18</v>
@@ -4080,8 +4153,13 @@
       <c r="I9" s="14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J9" s="1" t="str">
+        <f>_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A11,"&lt;/td&gt;&lt;td&gt;",B11,"&lt;/td&gt;&lt;td&gt;",C11,"&lt;/td&gt;&lt;td&gt;",D11,"&lt;/td&gt;&lt;td&gt;",G11,"&lt;/td&gt;&lt;td&gt;",H11,"&lt;/td&gt;&lt;td&gt;",I11,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;内部审计控制&lt;/td&gt;&lt;td&gt;E060&lt;/td&gt;&lt;td&gt;6-内审制度&lt;/td&gt;&lt;td&gt;内审制度&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="19.5" customHeight="1">
       <c r="A10" s="10" t="s">
         <v>61</v>
       </c>
@@ -4093,286 +4171,362 @@
       <c r="G10" s="11"/>
       <c r="H10" s="10"/>
       <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J10" s="1" t="str">
+        <f t="shared" ref="J10" si="0">_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A12,"&lt;/td&gt;&lt;td&gt;",B12,"&lt;/td&gt;&lt;td&gt;",C12,"&lt;/td&gt;&lt;td&gt;",D12,"&lt;/td&gt;&lt;td&gt;",G12,"&lt;/td&gt;&lt;td&gt;",H12,"&lt;/td&gt;&lt;td&gt;",I12,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;6-内审制度&lt;/td&gt;&lt;td&gt;E061&lt;/td&gt;&lt;td&gt;进出口内部审计&lt;/td&gt;&lt;td&gt;建立对进出口活动的内部审计制度并有效落实。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="36">
       <c r="A11" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" s="64" t="s">
-        <v>374</v>
-      </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="66"/>
+        <v>138</v>
+      </c>
+      <c r="D11" s="78" t="s">
+        <v>368</v>
+      </c>
+      <c r="E11" s="79"/>
+      <c r="F11" s="80"/>
       <c r="G11" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I11" s="19"/>
-    </row>
-    <row r="12" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J11" s="1" t="str">
+        <f>_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A11,"&lt;/td&gt;&lt;td&gt;",B11,"&lt;/td&gt;&lt;td&gt;",C11,"&lt;/td&gt;&lt;td&gt;",D11,"&lt;/td&gt;&lt;td&gt;",G11,"&lt;/td&gt;&lt;td&gt;",H11,"&lt;/td&gt;&lt;td&gt;",I11,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;内部审计控制&lt;/td&gt;&lt;td&gt;E060&lt;/td&gt;&lt;td&gt;6-内审制度&lt;/td&gt;&lt;td&gt;内审制度&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30.75" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D12" s="61" t="s">
-        <v>224</v>
-      </c>
-      <c r="E12" s="62"/>
-      <c r="F12" s="63"/>
+        <v>226</v>
+      </c>
+      <c r="D12" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="E12" s="67"/>
+      <c r="F12" s="68"/>
       <c r="G12" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I12" s="17"/>
-    </row>
-    <row r="13" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J12" s="1" t="str">
+        <f t="shared" ref="J12:J29" si="1">_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A12,"&lt;/td&gt;&lt;td&gt;",B12,"&lt;/td&gt;&lt;td&gt;",C12,"&lt;/td&gt;&lt;td&gt;",D12,"&lt;/td&gt;&lt;td&gt;",G12,"&lt;/td&gt;&lt;td&gt;",H12,"&lt;/td&gt;&lt;td&gt;",I12,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;6-内审制度&lt;/td&gt;&lt;td&gt;E061&lt;/td&gt;&lt;td&gt;进出口内部审计&lt;/td&gt;&lt;td&gt;建立对进出口活动的内部审计制度并有效落实。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="33.75" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="D13" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="E13" s="62"/>
-      <c r="F13" s="63"/>
+        <v>224</v>
+      </c>
+      <c r="D13" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="E13" s="67"/>
+      <c r="F13" s="68"/>
       <c r="G13" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J13" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;6-内审制度&lt;/td&gt;&lt;td&gt;E062&lt;/td&gt;&lt;td&gt;内部审计&lt;/td&gt;&lt;td&gt;每年实施1次以上的内部审计并建立书面或者电子资料的档案&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="45" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="D14" s="61" t="s">
-        <v>373</v>
-      </c>
-      <c r="E14" s="62"/>
-      <c r="F14" s="63"/>
+        <v>225</v>
+      </c>
+      <c r="D14" s="66" t="s">
+        <v>367</v>
+      </c>
+      <c r="E14" s="67"/>
+      <c r="F14" s="68"/>
       <c r="G14" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J14" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;6-内审制度&lt;/td&gt;&lt;td&gt;E063&lt;/td&gt;&lt;td&gt;高认内部审计&lt;/td&gt;&lt;td&gt;高认：已成为高级认证企业的，应当每年对持续符合海关高级认证企业标准实施内部审计。
+一般：已成为一般认证企业的，应当每年对持续符合海关一般认证企业标准实施内部审计。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="36">
       <c r="A15" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="D15" s="64" t="s">
-        <v>215</v>
-      </c>
-      <c r="E15" s="65"/>
-      <c r="F15" s="66"/>
+        <v>136</v>
+      </c>
+      <c r="D15" s="78" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="79"/>
+      <c r="F15" s="80"/>
       <c r="G15" s="37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J15" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;内部审计控制&lt;/td&gt;&lt;td&gt;E070&lt;/td&gt;&lt;td&gt;7-质量管理&lt;/td&gt;&lt;td&gt;建立对应的食品、化妆品、动植物及产品、工业品等法检商品质量安全管控制度，并有效落实。&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="64.5" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="68"/>
       <c r="G16" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I16" s="17"/>
-    </row>
-    <row r="17" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J16" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;7-质量管理&lt;/td&gt;&lt;td&gt;E071&lt;/td&gt;&lt;td&gt;特殊物品质量安全&lt;/td&gt;&lt;td&gt;根据出入境特殊物品风险等级，建立有效运行的生物安全管理体系，具备相应的生物安全控制能力。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="64.5" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="61" t="s">
+      <c r="D17" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="62"/>
-      <c r="F17" s="63"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="68"/>
       <c r="G17" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H17" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I17" s="17"/>
-    </row>
-    <row r="18" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J17" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;7-质量管理&lt;/td&gt;&lt;td&gt;E072&lt;/td&gt;&lt;td&gt;动植物质量安全&lt;/td&gt;&lt;td&gt;根据进出境动植物及其产品属性，建立有效运行的质量管理体系和疫情疫病防控制度，具备相应的风险管控处置能力。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="64.5" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="61" t="s">
+      <c r="D18" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="62"/>
-      <c r="F18" s="63"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="68"/>
       <c r="G18" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I18" s="17"/>
-    </row>
-    <row r="19" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J18" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;7-质量管理&lt;/td&gt;&lt;td&gt;E072&lt;/td&gt;&lt;td&gt;食品质量安全&lt;/td&gt;&lt;td&gt;企业进口食品的，建立境外出口商、境外食品生产企业实地审核制度，存留食品安全国家标准全项目自主检测报告。企业出口食品，具备与生产能力相适应的自检实验室，存留出厂检测报告。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="64.5" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="61" t="s">
+      <c r="D19" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="62"/>
-      <c r="F19" s="63"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="68"/>
       <c r="G19" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H19" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I19" s="17"/>
-    </row>
-    <row r="20" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J19" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;7-质量管理&lt;/td&gt;&lt;td&gt;E074&lt;/td&gt;&lt;td&gt;法定检验商品质量安全&lt;/td&gt;&lt;td&gt;根据质量安全风险，对法定检验商品建立有效运行的商品质量验收、检验检测、不合格处置、风险信息报告和风险消减等制度，具备质量安全相适应的企业自主管控能力。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="36">
       <c r="A20" s="20" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D20" s="78" t="s">
         <v>229</v>
       </c>
-      <c r="C20" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>231</v>
-      </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="80"/>
       <c r="G20" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H20" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I20" s="19"/>
-    </row>
-    <row r="21" spans="1:9" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J20" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;内部审计控制&lt;/td&gt;&lt;td&gt;E080&lt;/td&gt;&lt;td&gt;8-改进机制&lt;/td&gt;&lt;td&gt;改进机制&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="54.75" customHeight="1">
       <c r="A21" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D21" s="66" t="s">
         <v>230</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>232</v>
-      </c>
-      <c r="E21" s="62"/>
-      <c r="F21" s="63"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="68"/>
       <c r="G21" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J21" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;8-改进机制&lt;/td&gt;&lt;td&gt;E081&lt;/td&gt;&lt;td&gt;进出口改进&lt;/td&gt;&lt;td&gt;建立对进出口活动中已发现问题的改进机制和违法行为的责任追究机制并有效落实。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="64.5" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B22" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="D22" s="61" t="s">
-        <v>237</v>
-      </c>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
+      <c r="D22" s="66" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22" s="67"/>
+      <c r="F22" s="68"/>
       <c r="G22" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J22" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;8-改进机制&lt;/td&gt;&lt;td&gt;E082&lt;/td&gt;&lt;td&gt;改进实施&lt;/td&gt;&lt;td&gt;对海关要求的改正或者规范改进等事项，应当由法定代表人（负责人）或者负责关务的高级管理人员组织实施。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="10"/>
@@ -4382,144 +4536,181 @@
       <c r="G23" s="11"/>
       <c r="H23" s="10"/>
       <c r="I23" s="11"/>
-    </row>
-    <row r="24" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J23" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;信息系统控制-达标-0/基本达标-1/不达标-2/不适用-&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="36">
       <c r="A24" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D24" s="64" t="s">
-        <v>241</v>
-      </c>
-      <c r="E24" s="65"/>
-      <c r="F24" s="66"/>
+        <v>141</v>
+      </c>
+      <c r="D24" s="78" t="s">
+        <v>239</v>
+      </c>
+      <c r="E24" s="79"/>
+      <c r="F24" s="80"/>
       <c r="G24" s="42" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H24" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I24" s="19"/>
-    </row>
-    <row r="25" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J24" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;信息系统控制&lt;/td&gt;&lt;td&gt;E090&lt;/td&gt;&lt;td&gt;9-信息系统&lt;/td&gt;&lt;td&gt;具有管理企业生产经营活动的信息化系统。&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="36">
       <c r="A25" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="D25" s="64" t="s">
-        <v>242</v>
-      </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66"/>
+        <v>142</v>
+      </c>
+      <c r="D25" s="78" t="s">
+        <v>240</v>
+      </c>
+      <c r="E25" s="79"/>
+      <c r="F25" s="80"/>
       <c r="G25" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H25" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I25" s="19"/>
-    </row>
-    <row r="26" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J25" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;信息系统控制&lt;/td&gt;&lt;td&gt;E100&lt;/td&gt;&lt;td&gt;10-数据管理&lt;/td&gt;&lt;td&gt;建立信息系统的数据管理制度，数据存储3年以上。&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="36">
       <c r="A26" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D26" s="55" t="s">
-        <v>243</v>
-      </c>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57"/>
+        <v>143</v>
+      </c>
+      <c r="D26" s="72" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74"/>
       <c r="G26" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H26" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I26" s="19"/>
-    </row>
-    <row r="27" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J26" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;信息系统控制&lt;/td&gt;&lt;td&gt;E110&lt;/td&gt;&lt;td&gt;11-信息安全&lt;/td&gt;&lt;td&gt;信息安全&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="48">
       <c r="A27" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B27" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27" s="61" t="s">
-        <v>250</v>
-      </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63"/>
+      <c r="D27" s="66" t="s">
+        <v>248</v>
+      </c>
+      <c r="E27" s="67"/>
+      <c r="F27" s="68"/>
       <c r="G27" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I27" s="17"/>
-    </row>
-    <row r="28" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J27" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;11-信息安全&lt;/td&gt;&lt;td&gt;E111&lt;/td&gt;&lt;td&gt;信息安全制度&lt;/td&gt;&lt;td&gt;建立信息安全管理制度并有效落实&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="77.25" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B28" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="D28" s="61" t="s">
-        <v>251</v>
-      </c>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63"/>
+      <c r="D28" s="66" t="s">
+        <v>249</v>
+      </c>
+      <c r="E28" s="67"/>
+      <c r="F28" s="68"/>
       <c r="G28" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I28" s="17"/>
-    </row>
-    <row r="29" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J28" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;11-信息安全&lt;/td&gt;&lt;td&gt;E112&lt;/td&gt;&lt;td&gt;员工信息安全&lt;/td&gt;&lt;td&gt;对员工进行信息安全相关的培训。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="77.25" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="D29" s="61" t="s">
-        <v>252</v>
-      </c>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63"/>
+        <v>246</v>
+      </c>
+      <c r="D29" s="66" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" s="67"/>
+      <c r="F29" s="68"/>
       <c r="G29" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I29" s="17"/>
+      <c r="J29" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>&lt;tr&gt;&lt;td&gt;11-信息安全&lt;/td&gt;&lt;td&gt;E113&lt;/td&gt;&lt;td&gt;安全违约管理&lt;/td&gt;&lt;td&gt;对违反信息安全管理制度造成损害的行为应当予以责任追究。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4550,8 +4741,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2648A16A-9875-47F7-B2E8-6B667891C7C5}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
@@ -4561,7 +4753,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="5" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -4576,7 +4768,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="6"/>
@@ -4587,7 +4779,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
@@ -4600,38 +4792,38 @@
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E4" s="6"/>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="6"/>
       <c r="E5" s="6"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>254</v>
+        <v>146</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="6"/>
       <c r="C7" s="6"/>
       <c r="E7" s="6"/>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="14" t="s">
         <v>41</v>
       </c>
@@ -4641,13 +4833,13 @@
       <c r="C8" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="58" t="s">
+      <c r="D8" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="60"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="71"/>
       <c r="G8" s="45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H8" s="14" t="s">
         <v>18</v>
@@ -4656,9 +4848,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="19.5" customHeight="1">
       <c r="A9" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="10"/>
@@ -4668,52 +4860,68 @@
       <c r="G9" s="11"/>
       <c r="H9" s="10"/>
       <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="1:9" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J9" s="1" t="str">
+        <f>_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A10,"&lt;/td&gt;&lt;td&gt;",B10,"&lt;/td&gt;&lt;td&gt;",C10,"&lt;/td&gt;&lt;td&gt;",D10,"&lt;/td&gt;&lt;td&gt;",G10,"&lt;/td&gt;&lt;td&gt;",H10,"&lt;/td&gt;&lt;td&gt;",I10,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;财务状况标准&lt;/td&gt;&lt;td&gt;E120&lt;/td&gt;&lt;td&gt;12-会计信息&lt;/td&gt;&lt;td&gt;企业申请认证的，提交当年度会计师事务所审计报告，审计报告所反映的企业财务状况真实、完整、规范、合法；重新认证的，企业自成为高级认证企业起每年接受会计师事务所审计，审计报告所反映的企业财务状况真实、完整、规范、合法。&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="96" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="D10" s="76" t="s">
-        <v>257</v>
-      </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="78"/>
+        <v>252</v>
+      </c>
+      <c r="D10" s="81" t="s">
+        <v>255</v>
+      </c>
+      <c r="E10" s="82"/>
+      <c r="F10" s="83"/>
       <c r="G10" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J10" s="1" t="str">
+        <f>_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A10,"&lt;/td&gt;&lt;td&gt;",B10,"&lt;/td&gt;&lt;td&gt;",C10,"&lt;/td&gt;&lt;td&gt;",D10,"&lt;/td&gt;&lt;td&gt;",G10,"&lt;/td&gt;&lt;td&gt;",H10,"&lt;/td&gt;&lt;td&gt;",I10,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;财务状况标准&lt;/td&gt;&lt;td&gt;E120&lt;/td&gt;&lt;td&gt;12-会计信息&lt;/td&gt;&lt;td&gt;企业申请认证的，提交当年度会计师事务所审计报告，审计报告所反映的企业财务状况真实、完整、规范、合法；重新认证的，企业自成为高级认证企业起每年接受会计师事务所审计，审计报告所反映的企业财务状况真实、完整、规范、合法。&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="89.25" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="D11" s="76" t="s">
-        <v>259</v>
-      </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78"/>
+        <v>147</v>
+      </c>
+      <c r="D11" s="81" t="s">
+        <v>257</v>
+      </c>
+      <c r="E11" s="82"/>
+      <c r="F11" s="83"/>
       <c r="G11" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>60</v>
       </c>
       <c r="I11" s="19"/>
+      <c r="J11" s="1" t="str">
+        <f>_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A11,"&lt;/td&gt;&lt;td&gt;",B11,"&lt;/td&gt;&lt;td&gt;",C11,"&lt;/td&gt;&lt;td&gt;",D11,"&lt;/td&gt;&lt;td&gt;",G11,"&lt;/td&gt;&lt;td&gt;",H11,"&lt;/td&gt;&lt;td&gt;",I11,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;财务状况标准&lt;/td&gt;&lt;td&gt;E130&lt;/td&gt;&lt;td&gt;13-综合财务状况&lt;/td&gt;&lt;td&gt;企业在偿付、盈利、缴税能力方面整体状况良好，综合速动比率、现金流动负债比率、资产负债率、营业利润率、净资产收益率等财务状况在安全或者正常范围内。&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4728,11 +4936,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF6E2C6B-4019-4B01-9226-5CF587B95E65}">
-  <sheetPr>
+  <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.875" style="6" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
@@ -4745,7 +4953,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="5" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -4760,14 +4968,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="B2" s="7"/>
       <c r="D2" s="7"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
@@ -4780,66 +4988,72 @@
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="G7" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="C8" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C8" s="6" t="s">
-        <v>155</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="J11" s="1" t="str">
+        <f>_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A11,"&lt;/td&gt;&lt;td&gt;",B11,"&lt;/td&gt;&lt;td&gt;",C11,"&lt;/td&gt;&lt;td&gt;",D11,"&lt;/td&gt;&lt;td&gt;",G11,"&lt;/td&gt;&lt;td&gt;",H11,"&lt;/td&gt;&lt;td&gt;",I11,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1">
       <c r="A12" s="14" t="s">
         <v>41</v>
       </c>
@@ -4849,13 +5063,13 @@
       <c r="C12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="60"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="71"/>
       <c r="G12" s="38" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H12" s="14" t="s">
         <v>18</v>
@@ -4863,10 +5077,14 @@
       <c r="I12" s="14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J12" s="1" t="str">
+        <f t="shared" ref="J12:J40" si="0">_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A12,"&lt;/td&gt;&lt;td&gt;",B12,"&lt;/td&gt;&lt;td&gt;",C12,"&lt;/td&gt;&lt;td&gt;",D12,"&lt;/td&gt;&lt;td&gt;",G12,"&lt;/td&gt;&lt;td&gt;",H12,"&lt;/td&gt;&lt;td&gt;",I12,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;类别&lt;/td&gt;&lt;td&gt;代码&lt;/td&gt;&lt;td&gt;简称&lt;/td&gt;&lt;td&gt;标准说明&lt;/td&gt;&lt;td&gt;注意&lt;/td&gt;&lt;td&gt;评分&lt;/td&gt;&lt;td&gt;备注&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="10"/>
@@ -4876,54 +5094,67 @@
       <c r="G13" s="11"/>
       <c r="H13" s="10"/>
       <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;遵守法律法规-达标-0/基本达标-1/不达标-2/不适用-&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="36">
       <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="D14" s="76" t="s">
-        <v>385</v>
-      </c>
-      <c r="E14" s="77"/>
-      <c r="F14" s="78"/>
+        <v>149</v>
+      </c>
+      <c r="D14" s="81" t="s">
+        <v>379</v>
+      </c>
+      <c r="E14" s="82"/>
+      <c r="F14" s="83"/>
       <c r="G14" s="37" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;遵守法律法规&lt;/td&gt;&lt;td&gt;E140&lt;/td&gt;&lt;td&gt;14-人员守法&lt;/td&gt;&lt;td&gt;企业相关人员2年内【高认2年内，一般1年内】未因故意犯罪受过刑事处罚。&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="36.75" customHeight="1">
       <c r="A15" s="20" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="D15" s="76" t="s">
-        <v>268</v>
-      </c>
-      <c r="E15" s="77"/>
-      <c r="F15" s="78"/>
+        <v>262</v>
+      </c>
+      <c r="D15" s="81" t="s">
+        <v>263</v>
+      </c>
+      <c r="E15" s="82"/>
+      <c r="F15" s="83"/>
       <c r="G15" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;遵守法律法规&lt;/td&gt;&lt;td&gt;E150&lt;/td&gt;&lt;td&gt;15-企业守法&lt;/td&gt;&lt;td&gt;1年内被海关列入信用信息异常企业名录次数不超过1次，且不超过30日。&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="10"/>
@@ -4933,556 +5164,704 @@
       <c r="G16" s="11"/>
       <c r="H16" s="10"/>
       <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务规范-达标-0/基本达标-1/不达标-2/不适用-&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="36">
       <c r="A17" s="20" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="76" t="s">
-        <v>375</v>
-      </c>
-      <c r="E17" s="77"/>
-      <c r="F17" s="78"/>
+        <v>150</v>
+      </c>
+      <c r="D17" s="81" t="s">
+        <v>369</v>
+      </c>
+      <c r="E17" s="82"/>
+      <c r="F17" s="83"/>
       <c r="G17" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I17" s="19"/>
-    </row>
-    <row r="18" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务规范&lt;/td&gt;&lt;td&gt;E160&lt;/td&gt;&lt;td&gt;16-注册信息&lt;/td&gt;&lt;td&gt;在海关的注册登记或者备案信息与实际相符。&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="48">
       <c r="A18" s="20" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="D18" s="76" t="s">
-        <v>376</v>
-      </c>
-      <c r="E18" s="77"/>
-      <c r="F18" s="78"/>
+        <v>270</v>
+      </c>
+      <c r="D18" s="81" t="s">
+        <v>370</v>
+      </c>
+      <c r="E18" s="82"/>
+      <c r="F18" s="83"/>
       <c r="G18" s="44"/>
       <c r="H18" s="21" t="s">
         <v>60</v>
       </c>
       <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务规范&lt;/td&gt;&lt;td&gt;E170&lt;/td&gt;&lt;td&gt;17-进出口记录&lt;/td&gt;&lt;td&gt;2年内有进出口活动或者为进出口活动提供相关服务。&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="48">
       <c r="A19" s="20" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="D19" s="76" t="s">
-        <v>381</v>
-      </c>
-      <c r="E19" s="77"/>
-      <c r="F19" s="78"/>
+        <v>152</v>
+      </c>
+      <c r="D19" s="81" t="s">
+        <v>375</v>
+      </c>
+      <c r="E19" s="82"/>
+      <c r="F19" s="83"/>
       <c r="G19" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>60</v>
       </c>
       <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务规范&lt;/td&gt;&lt;td&gt;E180&lt;/td&gt;&lt;td&gt;18-申报规范&lt;/td&gt;&lt;td&gt;申报规范见单项标准。&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="71.25" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="61" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="62"/>
-      <c r="F20" s="63"/>
+      <c r="D20" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="67"/>
+      <c r="F20" s="68"/>
       <c r="G20" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H20" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I20" s="17"/>
-    </row>
-    <row r="21" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;18-申报规范&lt;/td&gt;&lt;td&gt;E181&lt;/td&gt;&lt;td&gt;查验率&lt;/td&gt;&lt;td&gt;连续4个季度【高级4个季度，一般认证2个季度】单季查获比率不超过同期全国平均查获比率&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="52.5" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="61" t="s">
+      <c r="D21" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="62"/>
-      <c r="F21" s="63"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="68"/>
       <c r="G21" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;18-申报规范&lt;/td&gt;&lt;td&gt;E182&lt;/td&gt;&lt;td&gt;核销情况&lt;/td&gt;&lt;td&gt;上年度及本年1至上月手（账）册未发生超期未报核的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="57.75" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="61" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
+      <c r="D22" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="67"/>
+      <c r="F22" s="68"/>
       <c r="G22" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;18-申报规范&lt;/td&gt;&lt;td&gt;E183&lt;/td&gt;&lt;td&gt;规范申报&lt;/td&gt;&lt;td&gt;连续4个季度【高级4个季度，一般认证2个季度】单季加工贸易手（账）册规范申报率超过同期全国平均手（账）册规范申报率。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="48">
       <c r="A23" s="20" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="D23" s="76" t="s">
-        <v>377</v>
-      </c>
-      <c r="E23" s="77"/>
-      <c r="F23" s="78"/>
+        <v>271</v>
+      </c>
+      <c r="D23" s="81" t="s">
+        <v>371</v>
+      </c>
+      <c r="E23" s="82"/>
+      <c r="F23" s="83"/>
       <c r="G23" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H23" s="21" t="s">
         <v>60</v>
       </c>
       <c r="I23" s="19"/>
-    </row>
-    <row r="24" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务规范&lt;/td&gt;&lt;td&gt;E190&lt;/td&gt;&lt;td&gt;19-传输规范&lt;/td&gt;&lt;td&gt;见单项标准。&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="59.25" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="D24" s="61" t="s">
-        <v>383</v>
-      </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="63"/>
+        <v>376</v>
+      </c>
+      <c r="D24" s="66" t="s">
+        <v>377</v>
+      </c>
+      <c r="E24" s="67"/>
+      <c r="F24" s="68"/>
       <c r="G24" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H24" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I24" s="17"/>
-    </row>
-    <row r="25" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;19-传输规范&lt;/td&gt;&lt;td&gt;E191&lt;/td&gt;&lt;td&gt;传输规范&lt;/td&gt;&lt;td&gt;连续4个季度单季舱单及相关电子数据传输差错率不超过同期全国平均传输差错率，连续4个季度单季运输工具进出境申报信息、转关单（载货清单）等物流信息的申报差错率不超过同期全国平均申报差错率。 　 　 &lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="48">
       <c r="A25" s="20" t="s">
         <v>30</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C25" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="D25" s="81" t="s">
         <v>279</v>
       </c>
-      <c r="D25" s="76" t="s">
-        <v>284</v>
-      </c>
-      <c r="E25" s="77"/>
-      <c r="F25" s="78"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="83"/>
       <c r="G25" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H25" s="21" t="s">
         <v>60</v>
       </c>
       <c r="I25" s="19"/>
-    </row>
-    <row r="26" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务规范&lt;/td&gt;&lt;td&gt;E200&lt;/td&gt;&lt;td&gt;20-税款缴纳&lt;/td&gt;&lt;td&gt;税款缴纳&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="77.25" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="D26" s="61" t="s">
-        <v>282</v>
-      </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63"/>
+        <v>278</v>
+      </c>
+      <c r="D26" s="66" t="s">
+        <v>277</v>
+      </c>
+      <c r="E26" s="67"/>
+      <c r="F26" s="68"/>
       <c r="G26" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H26" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I26" s="17"/>
-    </row>
-    <row r="27" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;20-税款缴纳&lt;/td&gt;&lt;td&gt;E201&lt;/td&gt;&lt;td&gt;税款罚款&lt;/td&gt;&lt;td&gt;认证期间，没有超过法定缴款期限尚未缴纳税款及罚没款项的情形。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="77.25" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="D27" s="61" t="s">
-        <v>384</v>
-      </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63"/>
+        <v>280</v>
+      </c>
+      <c r="D27" s="66" t="s">
+        <v>378</v>
+      </c>
+      <c r="E27" s="67"/>
+      <c r="F27" s="68"/>
       <c r="G27" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I27" s="17"/>
-    </row>
-    <row r="28" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;20-税款缴纳&lt;/td&gt;&lt;td&gt;E202&lt;/td&gt;&lt;td&gt;税款真实申报&lt;/td&gt;&lt;td&gt;高认：2年内无向海关提供虚假情况或者隐瞒事实的情形。
+一般：上年度以及本年度1月至上月滞纳税款报关单率不超过5%。   &lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="48">
       <c r="A28" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="C28" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D28" s="76" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78"/>
+      <c r="D28" s="81" t="s">
+        <v>155</v>
+      </c>
+      <c r="E28" s="82"/>
+      <c r="F28" s="83"/>
       <c r="G28" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H28" s="21" t="s">
         <v>60</v>
       </c>
       <c r="I28" s="19"/>
-    </row>
-    <row r="29" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;海关管理要求&lt;/td&gt;&lt;td&gt;E210&lt;/td&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;海关管理要求&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="77.25" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D29" s="61" t="s">
-        <v>386</v>
-      </c>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63"/>
+        <v>299</v>
+      </c>
+      <c r="D29" s="66" t="s">
+        <v>380</v>
+      </c>
+      <c r="E29" s="67"/>
+      <c r="F29" s="68"/>
       <c r="G29" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I29" s="17"/>
-    </row>
-    <row r="30" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E211&lt;/td&gt;&lt;td&gt;海关责令执行&lt;/td&gt;&lt;td&gt;2年内【高认2年内，一般1年内】无海关责令限期改正，但逾期不改正的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="77.25" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="D30" s="61" t="s">
-        <v>387</v>
-      </c>
-      <c r="E30" s="62"/>
-      <c r="F30" s="63"/>
+        <v>297</v>
+      </c>
+      <c r="D30" s="66" t="s">
+        <v>381</v>
+      </c>
+      <c r="E30" s="67"/>
+      <c r="F30" s="68"/>
       <c r="G30" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H30" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I30" s="17"/>
-    </row>
-    <row r="31" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E212&lt;/td&gt;&lt;td&gt;虚假申报&lt;/td&gt;&lt;td&gt;2年内【高认2年内，一般1年内】无向海关提供虚假情况或者隐瞒事实的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="77.25" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>388</v>
-      </c>
-      <c r="E31" s="62"/>
-      <c r="F31" s="63"/>
+        <v>298</v>
+      </c>
+      <c r="D31" s="66" t="s">
+        <v>382</v>
+      </c>
+      <c r="E31" s="67"/>
+      <c r="F31" s="68"/>
       <c r="G31" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H31" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I31" s="17"/>
-    </row>
-    <row r="32" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E213&lt;/td&gt;&lt;td&gt;海关指令执行&lt;/td&gt;&lt;td&gt;2年内【高认2年内，一般1年内】无由海关要求承担技术处理、退运、销毁等义务，但逾期不履行的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="77.25" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="D32" s="61" t="s">
-        <v>389</v>
-      </c>
-      <c r="E32" s="62"/>
-      <c r="F32" s="63"/>
+        <v>300</v>
+      </c>
+      <c r="D32" s="66" t="s">
+        <v>383</v>
+      </c>
+      <c r="E32" s="67"/>
+      <c r="F32" s="68"/>
       <c r="G32" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H32" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I32" s="17"/>
-    </row>
-    <row r="33" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E214&lt;/td&gt;&lt;td&gt;产品风险申报&lt;/td&gt;&lt;td&gt;2年内【高认2年内，一般1年内】无明知其产品存在风险未主动向海关报告相关信息，或者存在瞒报、漏报的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="77.25" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="D33" s="61" t="s">
-        <v>299</v>
-      </c>
-      <c r="E33" s="62"/>
-      <c r="F33" s="63"/>
+        <v>301</v>
+      </c>
+      <c r="D33" s="66" t="s">
+        <v>294</v>
+      </c>
+      <c r="E33" s="67"/>
+      <c r="F33" s="68"/>
       <c r="G33" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H33" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I33" s="17"/>
-    </row>
-    <row r="34" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E215&lt;/td&gt;&lt;td&gt;账簿单证执行&lt;/td&gt;&lt;td&gt;2年内无拒绝、拖延向海关提供账簿、单证或海关归类、价格、原产地、减免税核查所需资料等有关材料的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="77.25" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="D34" s="61" t="s">
-        <v>390</v>
-      </c>
-      <c r="E34" s="62"/>
-      <c r="F34" s="63"/>
+        <v>302</v>
+      </c>
+      <c r="D34" s="66" t="s">
+        <v>384</v>
+      </c>
+      <c r="E34" s="67"/>
+      <c r="F34" s="68"/>
       <c r="G34" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H34" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I34" s="17"/>
-    </row>
-    <row r="35" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E216&lt;/td&gt;&lt;td&gt;单证保管执行&lt;/td&gt;&lt;td&gt;2年内【高认2年内，一般1年内】无转移、隐匿、篡改、毁弃报关单证、进出口单证、合同、与进出口业务直接有关的其他资料的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="77.25" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D35" s="61" t="s">
-        <v>391</v>
-      </c>
-      <c r="E35" s="62"/>
-      <c r="F35" s="63"/>
+        <v>303</v>
+      </c>
+      <c r="D35" s="66" t="s">
+        <v>385</v>
+      </c>
+      <c r="E35" s="67"/>
+      <c r="F35" s="68"/>
       <c r="G35" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H35" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I35" s="17"/>
-    </row>
-    <row r="36" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E217&lt;/td&gt;&lt;td&gt;海关执法配合&lt;/td&gt;&lt;td&gt;2年内【高认2年内，一般1年内】无拒不配合海关执法的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="77.25" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B36" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="D36" s="66" t="s">
         <v>295</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="D36" s="61" t="s">
-        <v>300</v>
-      </c>
-      <c r="E36" s="62"/>
-      <c r="F36" s="63"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="68"/>
       <c r="G36" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H36" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I36" s="17"/>
-    </row>
-    <row r="37" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E218&lt;/td&gt;&lt;td&gt;保证金保函&lt;/td&gt;&lt;td&gt;2年内无未按海关要求办理保金保函的延期、退转手续的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="77.25" customHeight="1">
       <c r="A37" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="D37" s="61" t="s">
-        <v>392</v>
-      </c>
-      <c r="E37" s="62"/>
-      <c r="F37" s="63"/>
+        <v>305</v>
+      </c>
+      <c r="D37" s="66" t="s">
+        <v>386</v>
+      </c>
+      <c r="E37" s="67"/>
+      <c r="F37" s="68"/>
       <c r="G37" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H37" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I37" s="17"/>
-    </row>
-    <row r="38" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E219&lt;/td&gt;&lt;td&gt;行贿行为&lt;/td&gt;&lt;td&gt;2年内【高认2年内，一般1年内】无向海关人员行贿的行为。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="77.25" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="D38" s="61" t="s">
-        <v>301</v>
-      </c>
-      <c r="E38" s="62"/>
-      <c r="F38" s="63"/>
+        <v>306</v>
+      </c>
+      <c r="D38" s="66" t="s">
+        <v>296</v>
+      </c>
+      <c r="E38" s="67"/>
+      <c r="F38" s="68"/>
       <c r="G38" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H38" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I38" s="17"/>
-    </row>
-    <row r="39" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E21A&lt;/td&gt;&lt;td&gt;调查问卷&lt;/td&gt;&lt;td&gt;属于中国外贸出口先导指数样本企业的，1年内填报问卷及时率在90%以上、问卷答案与出口增速的吻合度在0.3以上的；属于进口货物使用去向调查样本企业、其他统计专项调查样本企业的，1年内填报问卷及时率和复核准确率在90%以上。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="77.25" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="D39" s="61" t="s">
-        <v>393</v>
-      </c>
-      <c r="E39" s="62"/>
-      <c r="F39" s="63"/>
+        <v>307</v>
+      </c>
+      <c r="D39" s="66" t="s">
+        <v>387</v>
+      </c>
+      <c r="E39" s="67"/>
+      <c r="F39" s="68"/>
       <c r="G39" s="43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H39" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I39" s="17"/>
-    </row>
-    <row r="40" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;21-海关管理要求&lt;/td&gt;&lt;td&gt;E21B&lt;/td&gt;&lt;td&gt;减免税货物&lt;/td&gt;&lt;td&gt;2年内【高认2年内，一般1年内】无未按规定向海关报告减免税货物使用状况的情形。&lt;/td&gt;&lt;td&gt;标准不同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="48">
       <c r="A40" s="20" t="s">
         <v>30</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="D40" s="76" t="s">
-        <v>394</v>
-      </c>
-      <c r="E40" s="77"/>
-      <c r="F40" s="78"/>
+        <v>282</v>
+      </c>
+      <c r="D40" s="81" t="s">
+        <v>388</v>
+      </c>
+      <c r="E40" s="82"/>
+      <c r="F40" s="83"/>
       <c r="G40" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H40" s="21" t="s">
         <v>60</v>
       </c>
       <c r="I40" s="19"/>
+      <c r="J40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进出口业务规范&lt;/td&gt;&lt;td&gt;E220&lt;/td&gt;&lt;td&gt;22-外部信用&lt;/td&gt;&lt;td&gt;企业和企业相关人员2年内【高认2年内，一般1年内】均未被列入国家失信联合惩戒名单。&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -5522,11 +5901,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DF4B9AC-787B-48FB-A501-2CC926B71567}">
-  <sheetPr>
+  <sheetPr codeName="Sheet7">
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
@@ -5538,7 +5917,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="5" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -5553,14 +5932,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="B2" s="7"/>
       <c r="D2" s="7"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
@@ -5573,41 +5952,41 @@
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="6" t="s">
         <v>96</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="6" t="s">
         <v>69</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="6" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="14" t="s">
         <v>41</v>
       </c>
@@ -5617,13 +5996,13 @@
       <c r="C10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="60"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="71"/>
       <c r="G10" s="38" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H10" s="14" t="s">
         <v>18</v>
@@ -5632,7 +6011,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="19.5" customHeight="1">
       <c r="A11" s="10" t="s">
         <v>74</v>
       </c>
@@ -5644,297 +6023,368 @@
       <c r="G11" s="11"/>
       <c r="H11" s="10"/>
       <c r="I11" s="11"/>
-    </row>
-    <row r="12" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J11" s="1" t="str">
+        <f>_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A11,"&lt;/td&gt;&lt;td&gt;",B11,"&lt;/td&gt;&lt;td&gt;",C11,"&lt;/td&gt;&lt;td&gt;",D11,"&lt;/td&gt;&lt;td&gt;",G11,"&lt;/td&gt;&lt;td&gt;",H11,"&lt;/td&gt;&lt;td&gt;",I11,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;贸易安全标准-达标-0/基本达标-1/不达标-2/不适用-&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="36">
       <c r="A12" s="20" t="s">
         <v>69</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>324</v>
-      </c>
-      <c r="E12" s="65"/>
-      <c r="F12" s="66"/>
+        <v>161</v>
+      </c>
+      <c r="D12" s="78" t="s">
+        <v>319</v>
+      </c>
+      <c r="E12" s="79"/>
+      <c r="F12" s="80"/>
       <c r="G12" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J12" s="1" t="str">
+        <f t="shared" ref="J12:J24" si="0">_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A12,"&lt;/td&gt;&lt;td&gt;",B12,"&lt;/td&gt;&lt;td&gt;",C12,"&lt;/td&gt;&lt;td&gt;",D12,"&lt;/td&gt;&lt;td&gt;",G12,"&lt;/td&gt;&lt;td&gt;",H12,"&lt;/td&gt;&lt;td&gt;",I12,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;场所安全&lt;/td&gt;&lt;td&gt;E230&lt;/td&gt;&lt;td&gt;23-场所安全&lt;/td&gt;&lt;td&gt;场所安全&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="48">
       <c r="A13" s="13" t="s">
         <v>70</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="D13" s="61" t="s">
-        <v>317</v>
-      </c>
-      <c r="E13" s="62"/>
-      <c r="F13" s="63"/>
+        <v>389</v>
+      </c>
+      <c r="D13" s="66" t="s">
+        <v>312</v>
+      </c>
+      <c r="E13" s="67"/>
+      <c r="F13" s="68"/>
       <c r="G13" s="41" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;10-场所安全&lt;/td&gt;&lt;td&gt;E231&lt;/td&gt;&lt;td&gt;场所安全制度&lt;/td&gt;&lt;td&gt;建立企业经营场所安全的管理制度并有效落实。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="66.75" customHeight="1">
       <c r="A14" s="13" t="s">
         <v>70</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="D14" s="61" t="s">
-        <v>318</v>
-      </c>
-      <c r="E14" s="62"/>
-      <c r="F14" s="63"/>
+        <v>390</v>
+      </c>
+      <c r="D14" s="66" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" s="67"/>
+      <c r="F14" s="68"/>
       <c r="G14" s="43" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;10-场所安全&lt;/td&gt;&lt;td&gt;E232&lt;/td&gt;&lt;td&gt;场所进出管理&lt;/td&gt;&lt;td&gt;企业经营场所应当具有相应设施防止未载明货物和未经许可人员进入。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="36">
       <c r="A15" s="20" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D15" s="64" t="s">
-        <v>325</v>
-      </c>
-      <c r="E15" s="65"/>
-      <c r="F15" s="66"/>
+        <v>163</v>
+      </c>
+      <c r="D15" s="78" t="s">
+        <v>320</v>
+      </c>
+      <c r="E15" s="79"/>
+      <c r="F15" s="80"/>
       <c r="G15" s="46" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I15" s="19"/>
-    </row>
-    <row r="16" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;进入安全&lt;/td&gt;&lt;td&gt;E240&lt;/td&gt;&lt;td&gt;24-进入安全&lt;/td&gt;&lt;td&gt;进入安全&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="26.25" customHeight="1">
       <c r="A16" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="D16" s="66" t="s">
         <v>326</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="D16" s="61" t="s">
-        <v>331</v>
-      </c>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="68"/>
       <c r="G16" s="43" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H16" s="18"/>
       <c r="I16" s="17"/>
-    </row>
-    <row r="17" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;24-进入安全&lt;/td&gt;&lt;td&gt;E241&lt;/td&gt;&lt;td&gt;人员车辆制度&lt;/td&gt;&lt;td&gt;建立人员和车辆出入管理制度并有效落实。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="57" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="D17" s="61" t="s">
-        <v>332</v>
-      </c>
-      <c r="E17" s="62"/>
-      <c r="F17" s="63"/>
+        <v>331</v>
+      </c>
+      <c r="D17" s="66" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17" s="67"/>
+      <c r="F17" s="68"/>
       <c r="G17" s="43" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H17" s="18"/>
       <c r="I17" s="17"/>
-    </row>
-    <row r="18" spans="1:9" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;24-进入安全&lt;/td&gt;&lt;td&gt;E242&lt;/td&gt;&lt;td&gt;出入权限管理&lt;/td&gt;&lt;td&gt;对企业员工进行身份识别和出入权限控制，限制未经授权员工进入敏感区域，对员工身份标识的发放和回收进行统一管理。员工的车辆进入企业应当停放在指定区域。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="56.25" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D18" s="61" t="s">
         <v>333</v>
       </c>
-      <c r="E18" s="62"/>
-      <c r="F18" s="63"/>
+      <c r="D18" s="66" t="s">
+        <v>328</v>
+      </c>
+      <c r="E18" s="67"/>
+      <c r="F18" s="68"/>
       <c r="G18" s="43" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H18" s="18"/>
       <c r="I18" s="17"/>
-    </row>
-    <row r="19" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;24-进入安全&lt;/td&gt;&lt;td&gt;E243&lt;/td&gt;&lt;td&gt;访客登记管理&lt;/td&gt;&lt;td&gt;实行访客登记管理，登记时必须检查带有照片的身份证件。访客进入企业应当佩戴临时身份标识，进入企业重点敏感区域应当有企业内部人员陪同。访客的车辆进入企业应当登记并停放在指定区域。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="44.25" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="D19" s="61" t="s">
         <v>334</v>
       </c>
-      <c r="E19" s="62"/>
-      <c r="F19" s="63"/>
+      <c r="D19" s="66" t="s">
+        <v>329</v>
+      </c>
+      <c r="E19" s="67"/>
+      <c r="F19" s="68"/>
       <c r="G19" s="43" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="H19" s="18"/>
       <c r="I19" s="17"/>
-    </row>
-    <row r="20" spans="1:9" ht="36" x14ac:dyDescent="0.2">
+      <c r="J19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;24-进入安全&lt;/td&gt;&lt;td&gt;E244&lt;/td&gt;&lt;td&gt;访客门禁管理&lt;/td&gt;&lt;td&gt;对未经许可进入、身份不明的人员能够识别并加以处置&lt;/td&gt;&lt;td&gt;一般认证无&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="36">
       <c r="A20" s="20" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
+        <v>166</v>
+      </c>
+      <c r="D20" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="E20" s="79"/>
+      <c r="F20" s="80"/>
       <c r="G20" s="46" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="H20" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I20" s="19"/>
-    </row>
-    <row r="21" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;人员安全&lt;/td&gt;&lt;td&gt;E250&lt;/td&gt;&lt;td&gt;25-人员安全&lt;/td&gt;&lt;td&gt;人员安全&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="52.5" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>341</v>
-      </c>
-      <c r="E21" s="62"/>
-      <c r="F21" s="63"/>
+        <v>344</v>
+      </c>
+      <c r="D21" s="66" t="s">
+        <v>336</v>
+      </c>
+      <c r="E21" s="67"/>
+      <c r="F21" s="68"/>
       <c r="G21" s="43" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;25-人员安全&lt;/td&gt;&lt;td&gt;E251&lt;/td&gt;&lt;td&gt;入职解聘管理&lt;/td&gt;&lt;td&gt;建立员工入职、离职停职等管理制度并有效执行。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="71.25" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="D22" s="61" t="s">
-        <v>342</v>
-      </c>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
+        <v>345</v>
+      </c>
+      <c r="D22" s="66" t="s">
+        <v>337</v>
+      </c>
+      <c r="E22" s="67"/>
+      <c r="F22" s="68"/>
       <c r="G22" s="43" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I22" s="17"/>
-    </row>
-    <row r="23" spans="1:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;25-人员安全&lt;/td&gt;&lt;td&gt;E252&lt;/td&gt;&lt;td&gt;员工档案管理&lt;/td&gt;&lt;td&gt;实行员工档案管理，具有动态的员工清单。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="57.75" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="D23" s="61" t="s">
-        <v>343</v>
-      </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="63"/>
+        <v>346</v>
+      </c>
+      <c r="D23" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="E23" s="67"/>
+      <c r="F23" s="68"/>
       <c r="G23" s="43" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H23" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I23" s="17"/>
-    </row>
-    <row r="24" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;25-人员安全&lt;/td&gt;&lt;td&gt;E253&lt;/td&gt;&lt;td&gt;入职核实管理&lt;/td&gt;&lt;td&gt;聘用员工前，核实应聘人员的身份、就业经历等信息，对拟聘用人员进行违法记录调查。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="52.5" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="D24" s="61" t="s">
-        <v>344</v>
-      </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="63"/>
+        <v>347</v>
+      </c>
+      <c r="D24" s="66" t="s">
+        <v>339</v>
+      </c>
+      <c r="E24" s="67"/>
+      <c r="F24" s="68"/>
       <c r="G24" s="43" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H24" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I24" s="17"/>
+      <c r="J24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;25-人员安全&lt;/td&gt;&lt;td&gt;E254&lt;/td&gt;&lt;td&gt;离职退出管理&lt;/td&gt;&lt;td&gt;对离职停职员工及时收回工作证件、设备，并禁止其进入企业经营场所及使用企业信息系统。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -5955,16 +6405,17 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{296EC222-C1FC-4007-BB49-9A5C26C6547E}">
-  <sheetPr>
+  <sheetPr codeName="Sheet8">
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
@@ -5976,7 +6427,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="5" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -5991,14 +6442,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="B2" s="7"/>
       <c r="D2" s="7"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
@@ -6011,56 +6462,62 @@
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="6" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="6" t="s">
         <v>72</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="6" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="J11" s="1" t="str">
+        <f>_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A11,"&lt;/td&gt;&lt;td&gt;",B11,"&lt;/td&gt;&lt;td&gt;",C11,"&lt;/td&gt;&lt;td&gt;",D11,"&lt;/td&gt;&lt;td&gt;",G11,"&lt;/td&gt;&lt;td&gt;",H11,"&lt;/td&gt;&lt;td&gt;",I11,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="14" t="s">
         <v>41</v>
       </c>
@@ -6070,13 +6527,13 @@
       <c r="C12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="60"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="71"/>
       <c r="G12" s="45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H12" s="14" t="s">
         <v>18</v>
@@ -6084,8 +6541,12 @@
       <c r="I12" s="14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J12" s="1" t="str">
+        <f t="shared" ref="J12:J33" si="0">_xlfn.CONCAT("&lt;tr&gt;&lt;td&gt;",A12,"&lt;/td&gt;&lt;td&gt;",B12,"&lt;/td&gt;&lt;td&gt;",C12,"&lt;/td&gt;&lt;td&gt;",D12,"&lt;/td&gt;&lt;td&gt;",G12,"&lt;/td&gt;&lt;td&gt;",H12,"&lt;/td&gt;&lt;td&gt;",I12,"&lt;/td&gt;&lt;/tr&gt;")</f>
+        <v>&lt;tr&gt;&lt;td&gt;类别&lt;/td&gt;&lt;td&gt;代码&lt;/td&gt;&lt;td&gt;简称&lt;/td&gt;&lt;td&gt;标准说明&lt;/td&gt;&lt;td&gt;注意&lt;/td&gt;&lt;td&gt;评分&lt;/td&gt;&lt;td&gt;备注&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>74</v>
       </c>
@@ -6097,109 +6558,127 @@
       <c r="G13" s="11"/>
       <c r="H13" s="10"/>
       <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;贸易安全标准-达标-0/基本达标-1/不达标-2/不适用-&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="42.75" customHeight="1">
       <c r="A14" s="20" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" s="64" t="s">
-        <v>316</v>
-      </c>
-      <c r="E14" s="65"/>
-      <c r="F14" s="66"/>
+        <v>167</v>
+      </c>
+      <c r="D14" s="78" t="s">
+        <v>311</v>
+      </c>
+      <c r="E14" s="79"/>
+      <c r="F14" s="80"/>
       <c r="G14" s="46" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;商业伙伴安全&lt;/td&gt;&lt;td&gt;E260&lt;/td&gt;&lt;td&gt;26-商业伙伴安全&lt;/td&gt;&lt;td&gt;建立评估、检查商业伙伴供应链安全的管理制度并有效落实。&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="52.5" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="61" t="s">
+      <c r="D15" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="63"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="68"/>
       <c r="G15" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I15" s="17"/>
-      <c r="J15" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;26-商业伙伴安全&lt;/td&gt;&lt;td&gt;E261&lt;/td&gt;&lt;td&gt;书面文件&lt;/td&gt;&lt;td&gt;书面文件：在合同、协议或者其他书面资料中要求商业伙伴按照本认证标准优化和完善贸易安全管理。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="71.25" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="62"/>
-      <c r="F16" s="63"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="68"/>
       <c r="G16" s="43" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I16" s="17"/>
-      <c r="J16" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;26-商业伙伴安全&lt;/td&gt;&lt;td&gt;E262&lt;/td&gt;&lt;td&gt;商品伙伴评估&lt;/td&gt;&lt;td&gt;全面评估：在筛选商业伙伴时根据本认证标准对商业伙伴进行全面评估，重点评估守法合规、贸易安全和供货资质，并有书面制度和程序。&lt;/td&gt;&lt;td&gt;一般认证没有&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="57.75" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="61" t="s">
+      <c r="D17" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="62"/>
-      <c r="F17" s="63"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="68"/>
       <c r="G17" s="43" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H17" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I17" s="17"/>
-      <c r="J17" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;26-商业伙伴安全&lt;/td&gt;&lt;td&gt;E263&lt;/td&gt;&lt;td&gt;监控检查&lt;/td&gt;&lt;td&gt;监控检查：定期监控或者检查商业伙伴遵守贸易安全要求的情况，并有书面制度和程序。&lt;/td&gt;&lt;td&gt;一般认证没有&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="10" t="s">
         <v>74</v>
       </c>
@@ -6211,351 +6690,441 @@
       <c r="G18" s="11"/>
       <c r="H18" s="10"/>
       <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+      <c r="J18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;贸易安全标准-达标-0/基本达标-1/不达标-2/不适用-&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="36">
       <c r="A19" s="20" t="s">
         <v>71</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="D19" s="76" t="s">
-        <v>353</v>
-      </c>
-      <c r="E19" s="77"/>
-      <c r="F19" s="78"/>
+        <v>349</v>
+      </c>
+      <c r="D19" s="81" t="s">
+        <v>348</v>
+      </c>
+      <c r="E19" s="82"/>
+      <c r="F19" s="83"/>
       <c r="G19" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;货品货物安全&lt;/td&gt;&lt;td&gt;E270&lt;/td&gt;&lt;td&gt;27-货品货物安全&lt;/td&gt;&lt;td&gt;建立保证进出口货物、进出境物品在运输、装卸和存储过程中的完整性、安全性的管理制度并有效落实。&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="63" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="62"/>
-      <c r="F20" s="63"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="68"/>
       <c r="G20" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H20" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I20" s="17"/>
-    </row>
-    <row r="21" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="J20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;27-货品货物安全&lt;/td&gt;&lt;td&gt;E271&lt;/td&gt;&lt;td&gt;装运和接收货物&lt;/td&gt;&lt;td&gt;装运和接收货物、物品：运抵的货物、物品要与货物、物品单证的信息相符，核实货物、物品的重量、标签、件数或者箱数。离岸的货物、物品要与购货订单或者装运订单上的内容进行核实。在货物、物品关键交接环节有签名、盖章等保护制度。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="48">
       <c r="A21" s="13" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="61" t="s">
+      <c r="D21" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="62"/>
-      <c r="F21" s="63"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="68"/>
       <c r="G21" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="J21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;27-货品货物安全&lt;/td&gt;&lt;td&gt;E272&lt;/td&gt;&lt;td&gt;货物差异&lt;/td&gt;&lt;td&gt;货物、物品差异：在出现货物、物品溢、短装，法检商品安全、卫生、环保等指标不合格或者其他异常现象时要及时报告或者采取其他应对措施，并有书面制度和程序。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="48">
       <c r="A22" s="13" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C22" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="52" t="s">
+      <c r="D22" s="86" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="53"/>
-      <c r="F22" s="54"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="88"/>
       <c r="G22" s="49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H22" s="50" t="s">
         <v>60</v>
       </c>
       <c r="I22" s="51"/>
-    </row>
-    <row r="23" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;27-货品货物安全&lt;/td&gt;&lt;td&gt;E273&lt;/td&gt;&lt;td&gt;出口安全&lt;/td&gt;&lt;td&gt;出口安全：生产型企业对出口货物、物品实施专人监装并保存相关记录；非生产型企业要求建立管理制度确保出口货物、物品安全装运。&lt;/td&gt;&lt;td&gt;一般认证没有&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="45" customHeight="1">
       <c r="A23" s="20" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="D23" s="76" t="s">
-        <v>360</v>
-      </c>
-      <c r="E23" s="79"/>
-      <c r="F23" s="80"/>
+        <v>169</v>
+      </c>
+      <c r="D23" s="81" t="s">
+        <v>355</v>
+      </c>
+      <c r="E23" s="84"/>
+      <c r="F23" s="85"/>
       <c r="G23" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H23" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I23" s="19"/>
-    </row>
-    <row r="24" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;集装箱安全&lt;/td&gt;&lt;td&gt;E280&lt;/td&gt;&lt;td&gt;28-集装箱安全&lt;/td&gt;&lt;td&gt;建立保证集装箱完整性、安全性的管理制度并有效落实&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="61.5" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="63"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="68"/>
       <c r="G24" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H24" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I24" s="17"/>
-    </row>
-    <row r="25" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="J24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;28-集装箱安全&lt;/td&gt;&lt;td&gt;E281&lt;/td&gt;&lt;td&gt;集装箱检查&lt;/td&gt;&lt;td&gt;集装箱检查：在装货前检查集装箱结构的物理完整性和可靠性，包括门的锁闭系统的可靠性，并做好相关登记。检查采取“七点检查法”（即对集装箱按照以下顺序检查：前壁、左侧、右侧、地板、顶部、内/外门、外部/起落架）。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="48">
       <c r="A25" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C25" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="D25" s="86" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="53"/>
-      <c r="F25" s="54"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="88"/>
       <c r="G25" s="49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H25" s="50" t="s">
         <v>60</v>
       </c>
       <c r="I25" s="51"/>
-    </row>
-    <row r="26" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="J25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;28-集装箱安全&lt;/td&gt;&lt;td&gt;E282&lt;/td&gt;&lt;td&gt;集装箱封条&lt;/td&gt;&lt;td&gt;集装箱封条：已装货集装箱要施加高安全度的封条，所有封条都要符合或者超出现行PAS ISO 17712对高度安全封条的标准，封条有专人管理、登记。要建立施加和检验封条的书面制度和程序，以及封条异常的报告机制。进出境厢式货车应全程施加封条，确保安全。&lt;/td&gt;&lt;td&gt;一般认证没有&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="48">
       <c r="A26" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C26" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="52" t="s">
+      <c r="D26" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="53"/>
-      <c r="F26" s="54"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="88"/>
       <c r="G26" s="49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H26" s="50" t="s">
         <v>60</v>
       </c>
       <c r="I26" s="51"/>
-    </row>
-    <row r="27" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;28-集装箱安全&lt;/td&gt;&lt;td&gt;E283&lt;/td&gt;&lt;td&gt;集装箱存储&lt;/td&gt;&lt;td&gt;集装箱存储：集装箱要保存在安全的区域，以防止未经许可的进入或者改装，有报告和解决未经许可擅自进入集装箱或者集装箱存储区域的程序。&lt;/td&gt;&lt;td&gt;一般认证没有&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="45" customHeight="1">
       <c r="A27" s="20" t="s">
         <v>73</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="D27" s="76" t="s">
-        <v>359</v>
-      </c>
-      <c r="E27" s="79"/>
-      <c r="F27" s="80"/>
+        <v>170</v>
+      </c>
+      <c r="D27" s="81" t="s">
+        <v>354</v>
+      </c>
+      <c r="E27" s="84"/>
+      <c r="F27" s="85"/>
       <c r="G27" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="19"/>
-    </row>
-    <row r="28" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="J27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;运输工具安全&lt;/td&gt;&lt;td&gt;E290&lt;/td&gt;&lt;td&gt;29-运输工具安全&lt;/td&gt;&lt;td&gt;建立保证运输工具的完整性、安全性的管理制度并有效落实&lt;/td&gt;&lt;td&gt;D&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="48">
       <c r="A28" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="68"/>
       <c r="G28" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H28" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I28" s="17"/>
-    </row>
-    <row r="29" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="J28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;29-运输工具安全&lt;/td&gt;&lt;td&gt;E291&lt;/td&gt;&lt;td&gt;运输工具检查&lt;/td&gt;&lt;td&gt;运输工具检查：对所有运输进出口货物、物品的运输工具进行检查，防止藏匿可疑货物、物品，并有书面制度和程序。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="48">
       <c r="A29" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C29" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D29" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="53"/>
-      <c r="F29" s="54"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="88"/>
       <c r="G29" s="49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H29" s="50" t="s">
         <v>60</v>
       </c>
       <c r="I29" s="51"/>
-    </row>
-    <row r="30" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;29-运输工具安全&lt;/td&gt;&lt;td&gt;E292&lt;/td&gt;&lt;td&gt;运输工具存储&lt;/td&gt;&lt;td&gt;运输工具存储：运输工具要停放在安全的区域，以防止未经许可的进入或者其他损害，有报告和解决未经许可擅自进入或者损害的程序。&lt;/td&gt;&lt;td&gt;一般认证没有&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="45" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="D30" s="76" t="s">
-        <v>359</v>
-      </c>
-      <c r="E30" s="79"/>
-      <c r="F30" s="80"/>
+        <v>398</v>
+      </c>
+      <c r="D30" s="81" t="s">
+        <v>354</v>
+      </c>
+      <c r="E30" s="84"/>
+      <c r="F30" s="85"/>
       <c r="G30" s="44" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>44</v>
       </c>
       <c r="I30" s="19"/>
-    </row>
-    <row r="31" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="J30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;危机管理控制&lt;/td&gt;&lt;td&gt;E300&lt;/td&gt;&lt;td&gt;30-危机管理&lt;/td&gt;&lt;td&gt;建立保证运输工具的完整性、安全性的管理制度并有效落实&lt;/td&gt;&lt;td&gt;S&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="48">
       <c r="A31" s="13" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>407</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>405</v>
-      </c>
-      <c r="E31" s="62"/>
-      <c r="F31" s="63"/>
+        <v>401</v>
+      </c>
+      <c r="D31" s="66" t="s">
+        <v>399</v>
+      </c>
+      <c r="E31" s="67"/>
+      <c r="F31" s="68"/>
       <c r="G31" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H31" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I31" s="17"/>
-    </row>
-    <row r="32" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="J31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;30-危机管理&lt;/td&gt;&lt;td&gt;E301&lt;/td&gt;&lt;td&gt;应急预案&lt;/td&gt;&lt;td&gt;建立应对灾害、紧急情况的应急预案。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="48">
       <c r="A32" s="13" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="D32" s="61" t="s">
-        <v>406</v>
-      </c>
-      <c r="E32" s="62"/>
-      <c r="F32" s="63"/>
+        <v>402</v>
+      </c>
+      <c r="D32" s="66" t="s">
+        <v>400</v>
+      </c>
+      <c r="E32" s="67"/>
+      <c r="F32" s="68"/>
       <c r="G32" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H32" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I32" s="17"/>
-    </row>
-    <row r="33" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="J32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;30-危机管理&lt;/td&gt;&lt;td&gt;E302&lt;/td&gt;&lt;td&gt;供应链风险培训&lt;/td&gt;&lt;td&gt;定期对员工进行与国际贸易供应链中货物流动相关风险的教育和培训，让员工了解、掌握海关认证企业在保证货物安全过程中应做的工作。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="48">
       <c r="A33" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="D33" s="66" t="s">
         <v>404</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="D33" s="61" t="s">
-        <v>410</v>
-      </c>
-      <c r="E33" s="62"/>
-      <c r="F33" s="63"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="68"/>
       <c r="G33" s="43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H33" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I33" s="17"/>
+      <c r="J33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>&lt;tr&gt;&lt;td&gt;30-危机管理&lt;/td&gt;&lt;td&gt;E303&lt;/td&gt;&lt;td&gt;员工风险培训&lt;/td&gt;&lt;td&gt;定期对员工进行危机管理的培训和危机处理模拟演练，让员工了解、掌握在应急处置和异常报告过程中应做的工作。&lt;/td&gt;&lt;td&gt;标准相同&lt;/td&gt;&lt;td&gt;下拉框
+0/-1/-2/不适用/不确定，默认是0
+不参与计算&lt;/td&gt;&lt;td&gt;&lt;/td&gt;&lt;/tr&gt;</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">
